--- a/artfynd/A 21519-2025 artfynd.xlsx
+++ b/artfynd/A 21519-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>7002296</v>
       </c>
       <c r="B2" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422369.0264420317</v>
+        <v>422369</v>
       </c>
       <c r="R2" t="n">
-        <v>6968092.616018423</v>
+        <v>6968093</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2013-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7002286</v>
+        <v>7002284</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422514.0119634692</v>
+        <v>422543</v>
       </c>
       <c r="R3" t="n">
-        <v>6967874.338620347</v>
+        <v>6967641</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2013-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7002372</v>
+        <v>7002286</v>
       </c>
       <c r="B4" t="n">
-        <v>90699</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>232140</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422290.3291514791</v>
+        <v>422514</v>
       </c>
       <c r="R4" t="n">
-        <v>6968074.824085486</v>
+        <v>6967874</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2013-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7002293</v>
+        <v>7002287</v>
       </c>
       <c r="B5" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422192.4570189495</v>
+        <v>422501</v>
       </c>
       <c r="R5" t="n">
-        <v>6968078.516060066</v>
+        <v>6967919</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2013-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7002284</v>
+        <v>7002289</v>
       </c>
       <c r="B6" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422542.8344218575</v>
+        <v>422461</v>
       </c>
       <c r="R6" t="n">
-        <v>6967640.965696576</v>
+        <v>6967941</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,19 +1147,9 @@
           <t>2013-09-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2013-09-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7002288</v>
+        <v>7002294</v>
       </c>
       <c r="B7" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>422479.2428537359</v>
+        <v>422199</v>
       </c>
       <c r="R7" t="n">
-        <v>6967914.016885693</v>
+        <v>6968073</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,19 +1248,9 @@
           <t>2013-09-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2013-09-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7002287</v>
+        <v>7002292</v>
       </c>
       <c r="B8" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>422501.3226086574</v>
+        <v>422201</v>
       </c>
       <c r="R8" t="n">
-        <v>6967918.523533902</v>
+        <v>6968065</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1444,19 +1349,9 @@
           <t>2013-09-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2013-09-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7002294</v>
+        <v>7002293</v>
       </c>
       <c r="B9" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1503</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1527,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>422198.7427694099</v>
+        <v>422192</v>
       </c>
       <c r="R9" t="n">
-        <v>6968073.338680363</v>
+        <v>6968079</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1560,19 +1450,9 @@
           <t>2013-09-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2013-09-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7002292</v>
+        <v>7002288</v>
       </c>
       <c r="B10" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1643,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>422200.8243393743</v>
+        <v>422479</v>
       </c>
       <c r="R10" t="n">
-        <v>6968064.604119173</v>
+        <v>6967914</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1676,19 +1551,9 @@
           <t>2013-09-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2013-09-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1719,37 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7002289</v>
+        <v>7002372</v>
       </c>
       <c r="B11" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>232140</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1759,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>422461.1110065142</v>
+        <v>422290</v>
       </c>
       <c r="R11" t="n">
-        <v>6967940.959192312</v>
+        <v>6968075</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1792,19 +1652,9 @@
           <t>2013-09-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2013-09-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
